--- a/Capraz_Satis_Firsatlari.xlsx
+++ b/Capraz_Satis_Firsatlari.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C298" s="6" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C302" s="6" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C195" s="8" t="n">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C198" s="8" t="n">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Kural</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="C228" s="8" t="n">
